--- a/Baigiamojo_darbo_vertinimo_lentele.xlsx
+++ b/Baigiamojo_darbo_vertinimo_lentele.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JustinasKrutikovas\Desktop\GEN AI 26 05 18 PRE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JustinasKrutikovas\Desktop\GEN AI 26 05 18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E5F995-98A2-4D45-90DD-3D0491005E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016802EC-FACF-421C-8A5B-7E0E3E8B7F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
   <si>
     <t>Generatyvusis DI pradedantiesiems — Baigiamojo darbo vertinimo lentelė</t>
   </si>
@@ -334,6 +334,27 @@
   </si>
   <si>
     <t>n8n/Vibe-coding: vibe-coding patirtis arba pamokos/ateities plėtra  |  Tyrimas: išvados ir patarimai kolegoms</t>
+  </si>
+  <si>
+    <t>Laikys testą</t>
+  </si>
+  <si>
+    <t>Laikys abu</t>
+  </si>
+  <si>
+    <t>Laikys testą, jei BD nepasiseks</t>
+  </si>
+  <si>
+    <t>Dokumentų formavimas, vadovo kūrimas darželio pedagogams</t>
+  </si>
+  <si>
+    <t>Įskaityta</t>
+  </si>
+  <si>
+    <t>1. Tyrimas</t>
+  </si>
+  <si>
+    <t>Skyrė nemažai laiko</t>
   </si>
 </sst>
 </file>
@@ -424,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -463,6 +484,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -807,7 +831,7 @@
     <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
@@ -816,7 +840,7 @@
     <col min="11" max="11" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -954,7 +978,7 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4" t="str">
-        <f t="shared" ref="K6:K20" si="0">IF(COUNT(G7:J7)=4,SUM(G7:J7),"")</f>
+        <f t="shared" ref="K7:K20" si="0">IF(COUNT(G7:J7)=4,SUM(G7:J7),"")</f>
         <v/>
       </c>
       <c r="L7" s="4"/>
@@ -1005,7 +1029,9 @@
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
-      <c r="N9" s="5"/>
+      <c r="N9" s="5" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1065,7 +1091,6 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="str">
@@ -1083,21 +1108,43 @@
       <c r="B13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4" t="str">
+      <c r="C13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="16">
+        <v>46212</v>
+      </c>
+      <c r="F13" s="4">
+        <v>10</v>
+      </c>
+      <c r="G13" s="4">
+        <v>2</v>
+      </c>
+      <c r="H13" s="2">
+        <v>5</v>
+      </c>
+      <c r="I13" s="4">
+        <v>3</v>
+      </c>
+      <c r="J13" s="4">
+        <v>4</v>
+      </c>
+      <c r="K13" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="5"/>
+        <v>14</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1166,7 +1213,9 @@
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
-      <c r="N16" s="3"/>
+      <c r="N16" s="3" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
@@ -1189,7 +1238,9 @@
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="5"/>
+      <c r="N17" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="18" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1212,7 +1263,6 @@
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
-      <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
@@ -1307,7 +1357,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C6:C20" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1. Tyrimas,2. n8n automatizacija,2. Vibe-coding"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G6:G20 H6:H20 I6:I20 J6:J20" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G6:G20 I6:J20 H6:H11 H13:H20" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="L6:L20" xr:uid="{00000000-0002-0000-0000-000002000000}">

--- a/Baigiamojo_darbo_vertinimo_lentele.xlsx
+++ b/Baigiamojo_darbo_vertinimo_lentele.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JustinasKrutikovas\Desktop\GEN AI 26 05 18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016802EC-FACF-421C-8A5B-7E0E3E8B7F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FE8FE7-B02C-4F5C-B355-78866A939D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="79">
   <si>
     <t>Generatyvusis DI pradedantiesiems — Baigiamojo darbo vertinimo lentelė</t>
   </si>
@@ -355,6 +355,15 @@
   </si>
   <si>
     <t>Skyrė nemažai laiko</t>
+  </si>
+  <si>
+    <t>Praktinis darbas</t>
+  </si>
+  <si>
+    <t>Klientų registracijos sistema</t>
+  </si>
+  <si>
+    <t>Automatizacija</t>
   </si>
 </sst>
 </file>
@@ -468,6 +477,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -484,9 +496,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -830,7 +839,7 @@
   <cols>
     <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
     <col min="4" max="4" width="63.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -844,59 +853,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
     </row>
     <row r="5" spans="1:15" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -960,7 +969,9 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="3"/>
+      <c r="N6" s="3" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
@@ -1063,21 +1074,43 @@
       <c r="B11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4" t="str">
+      <c r="C11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="8">
+        <v>46218</v>
+      </c>
+      <c r="F11" s="4">
+        <v>10</v>
+      </c>
+      <c r="G11" s="4">
+        <v>4</v>
+      </c>
+      <c r="H11" s="4">
+        <v>2</v>
+      </c>
+      <c r="I11" s="4">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4">
+        <v>2</v>
+      </c>
+      <c r="K11" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1114,7 +1147,7 @@
       <c r="D13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="8">
         <v>46212</v>
       </c>
       <c r="F13" s="4">
@@ -1311,22 +1344,22 @@
       <c r="N20" s="3"/>
     </row>
     <row r="22" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1382,16 +1415,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="12"/>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="14"/>
+      <c r="B3" s="15"/>
     </row>
     <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
@@ -1446,10 +1479,10 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="14"/>
+      <c r="B11" s="15"/>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -1468,10 +1501,10 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="14"/>
+      <c r="B14" s="15"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -1490,10 +1523,10 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="14"/>
+      <c r="B17" s="15"/>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
@@ -1516,10 +1549,10 @@
       <c r="B20" s="7"/>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="14"/>
+      <c r="B21" s="15"/>
     </row>
     <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">

--- a/Baigiamojo_darbo_vertinimo_lentele.xlsx
+++ b/Baigiamojo_darbo_vertinimo_lentele.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JustinasKrutikovas\Desktop\GEN AI 26 05 18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FE8FE7-B02C-4F5C-B355-78866A939D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E7D9C7-38C2-4828-84CC-E1A6838053F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1090,17 +1090,17 @@
         <v>4</v>
       </c>
       <c r="H11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L11" s="4">
         <v>0</v>

--- a/Baigiamojo_darbo_vertinimo_lentele.xlsx
+++ b/Baigiamojo_darbo_vertinimo_lentele.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JustinasKrutikovas\Desktop\GEN AI 26 05 18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E7D9C7-38C2-4828-84CC-E1A6838053F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BF38A6-53D2-4D34-B702-98AD36BAE17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="80">
   <si>
     <t>Generatyvusis DI pradedantiesiems — Baigiamojo darbo vertinimo lentelė</t>
   </si>
@@ -364,6 +364,9 @@
   </si>
   <si>
     <t>Automatizacija</t>
+  </si>
+  <si>
+    <t>Instagram postų kūrimas su AI</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1020,9 @@
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-      <c r="N8" s="3"/>
+      <c r="N8" s="3" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
@@ -1259,16 +1264,6 @@
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="3" t="s">
@@ -1282,20 +1277,38 @@
       <c r="B18" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="C18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="8">
+        <v>46223</v>
+      </c>
+      <c r="F18" s="4">
+        <v>10</v>
+      </c>
+      <c r="G18" s="4">
+        <v>5</v>
+      </c>
+      <c r="H18" s="4">
+        <v>3</v>
+      </c>
+      <c r="I18" s="4">
+        <v>5</v>
+      </c>
+      <c r="J18" s="4">
+        <v>4</v>
+      </c>
+      <c r="K18" s="4">
+        <f>IF(COUNT(G18:J18)=4,SUM(G18:J18),"")</f>
+        <v>17</v>
       </c>
       <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="M18" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
@@ -1318,7 +1331,9 @@
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
-      <c r="N19" s="5"/>
+      <c r="N19" s="5" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="20" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -1367,7 +1382,7 @@
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A22:N22"/>
   </mergeCells>
-  <conditionalFormatting sqref="K6:K20">
+  <conditionalFormatting sqref="K6:K16 K18:K20">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
       <formula>12</formula>
     </cfRule>
@@ -1390,7 +1405,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C6:C20" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1. Tyrimas,2. n8n automatizacija,2. Vibe-coding"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G6:G20 I6:J20 H6:H11 H13:H20" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H6:H11 H13:H16 G18:J20 I6:J16 G6:G16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="L6:L20" xr:uid="{00000000-0002-0000-0000-000002000000}">

--- a/Baigiamojo_darbo_vertinimo_lentele.xlsx
+++ b/Baigiamojo_darbo_vertinimo_lentele.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JustinasKrutikovas\Desktop\GEN AI 26 05 18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BF38A6-53D2-4D34-B702-98AD36BAE17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DFA182-095B-46B0-A927-650BF2065AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38295" yWindow="7260" windowWidth="16410" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vertinimo lentelė" sheetId="1" r:id="rId1"/>
@@ -101,27 +101,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Privaloma TIK jei Variantas 2 ir sprendimas sukurtas 'vibe-coding' būdu (GitHub Copilot, Lovable.dev, OpenAI Codex ir kt.).
-Pažymėti N/A, jei šis reikalavimas netaikomas (n8n arba Tyrimas).</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
   <si>
     <t>Generatyvusis DI pradedantiesiems — Baigiamojo darbo vertinimo lentelė</t>
   </si>
@@ -167,10 +152,6 @@
 (iš 20)</t>
   </si>
   <si>
-    <t>Vibe-coding mini-
-pranešimas (2 min)</t>
-  </si>
-  <si>
     <t>Galutinis rezultatas</t>
   </si>
   <si>
@@ -367,13 +348,19 @@
   </si>
   <si>
     <t>Instagram postų kūrimas su AI</t>
+  </si>
+  <si>
+    <t>Testo balai</t>
+  </si>
+  <si>
+    <t>Balas Dešimbalėje sistemoje</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,8 +398,22 @@
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,6 +428,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -454,10 +465,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -471,16 +484,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -499,8 +512,26 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
@@ -837,25 +868,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="63.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -873,8 +905,9 @@
       <c r="M1" s="10"/>
       <c r="N1" s="10"/>
       <c r="O1" s="10"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" s="10"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -890,8 +923,9 @@
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
-    </row>
-    <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P2" s="10"/>
+    </row>
+    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
@@ -909,8 +943,9 @@
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
-    </row>
-    <row r="5" spans="1:15" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P3" s="12"/>
+    </row>
+    <row r="5" spans="1:16" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -942,425 +977,622 @@
         <v>11</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:16" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
+        <v>1</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17">
+        <v>0</v>
+      </c>
+      <c r="H6" s="17">
+        <v>0</v>
+      </c>
+      <c r="I6" s="17">
+        <v>0</v>
+      </c>
+      <c r="J6" s="17">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17">
+        <v>23</v>
+      </c>
+      <c r="L6" s="17">
+        <f>ROUND(0.8*K6,0)</f>
+        <v>18</v>
+      </c>
+      <c r="M6" s="17">
+        <f>ROUND(L6/2,0)</f>
+        <v>9</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4" t="str">
-        <f t="shared" ref="K7:K20" si="0">IF(COUNT(G7:J7)=4,SUM(G7:J7),"")</f>
-        <v/>
-      </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="5"/>
-    </row>
-    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" ref="M7:M20" si="0">ROUND(L7/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="7"/>
+    </row>
+    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2" t="str">
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4" t="str">
+      <c r="B9" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17">
+        <v>0</v>
+      </c>
+      <c r="H9" s="17">
+        <v>0</v>
+      </c>
+      <c r="I9" s="17">
+        <v>0</v>
+      </c>
+      <c r="J9" s="17">
+        <v>0</v>
+      </c>
+      <c r="K9" s="17">
+        <v>16</v>
+      </c>
+      <c r="L9" s="17">
+        <f>ROUND(0.8*K9,0)</f>
+        <v>13</v>
+      </c>
+      <c r="M9" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" s="18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="4"/>
+      <c r="O10" s="7"/>
+    </row>
+    <row r="11" spans="1:16" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>6</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2" t="str">
+      <c r="C11" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="19">
+        <v>46218</v>
+      </c>
+      <c r="F11" s="17">
+        <v>10</v>
+      </c>
+      <c r="G11" s="17">
+        <v>4</v>
+      </c>
+      <c r="H11" s="17">
+        <v>3</v>
+      </c>
+      <c r="I11" s="17">
+        <v>4</v>
+      </c>
+      <c r="J11" s="17">
+        <v>3</v>
+      </c>
+      <c r="K11" s="17">
+        <v>0</v>
+      </c>
+      <c r="L11" s="17">
+        <f>IF(COUNT(G11:J11)=4,SUM(G11:J11),"")</f>
+        <v>14</v>
+      </c>
+      <c r="M11" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>6</v>
-      </c>
-      <c r="B11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O11" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>7</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="8">
-        <v>46218</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N12" s="4"/>
+      <c r="O12" s="7"/>
+    </row>
+    <row r="13" spans="1:16" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="19">
+        <v>46212</v>
+      </c>
+      <c r="F13" s="17">
         <v>10</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G13" s="17">
+        <v>2</v>
+      </c>
+      <c r="H13" s="17">
+        <v>5</v>
+      </c>
+      <c r="I13" s="17">
+        <v>3</v>
+      </c>
+      <c r="J13" s="17">
         <v>4</v>
       </c>
-      <c r="H11" s="4">
-        <v>3</v>
-      </c>
-      <c r="I11" s="4">
-        <v>4</v>
-      </c>
-      <c r="J11" s="4">
-        <v>3</v>
-      </c>
-      <c r="K11" s="4">
+      <c r="K13" s="17">
+        <v>0</v>
+      </c>
+      <c r="L13" s="17">
+        <f>IF(COUNT(G13:J13)=4,SUM(G13:J13),"")</f>
+        <v>14</v>
+      </c>
+      <c r="M13" s="17">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="L11" s="4">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2" t="str">
+      <c r="N13" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O13" s="18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>8</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="8">
-        <v>46212</v>
-      </c>
-      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4"/>
+      <c r="O14" s="7"/>
+    </row>
+    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
         <v>10</v>
       </c>
-      <c r="G13" s="4">
-        <v>2</v>
-      </c>
-      <c r="H13" s="2">
-        <v>5</v>
-      </c>
-      <c r="I13" s="4">
-        <v>3</v>
-      </c>
-      <c r="J13" s="4">
-        <v>4</v>
-      </c>
-      <c r="K13" s="4">
+      <c r="B15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="L13" s="4">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>9</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>10</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="5"/>
-    </row>
-    <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4"/>
+      <c r="O15" s="7"/>
+    </row>
+    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="3"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2" t="str">
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4"/>
+      <c r="O16" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
         <v>12</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="18"/>
+      <c r="G17" s="20">
+        <v>0</v>
+      </c>
+      <c r="H17" s="17">
+        <v>0</v>
+      </c>
+      <c r="I17" s="17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="21">
+        <v>20</v>
+      </c>
+      <c r="L17" s="22">
+        <f>ROUND(0.8*K17,0)</f>
+        <v>16</v>
+      </c>
+      <c r="M17" s="17">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O17" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>13</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>13</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="8">
+      <c r="C18" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="19">
         <v>46223</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="17">
         <v>10</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="17">
         <v>5</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="17">
         <v>3</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="17">
         <v>5</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="17">
         <v>4</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="17">
+        <v>0</v>
+      </c>
+      <c r="L18" s="17">
         <f>IF(COUNT(G18:J18)=4,SUM(G18:J18),"")</f>
         <v>17</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="M18" s="17">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
         <v>14</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4" t="str">
+      <c r="B19" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17">
+        <v>0</v>
+      </c>
+      <c r="H19" s="17">
+        <v>0</v>
+      </c>
+      <c r="I19" s="17">
+        <v>0</v>
+      </c>
+      <c r="J19" s="17">
+        <v>0</v>
+      </c>
+      <c r="K19" s="17">
+        <v>20</v>
+      </c>
+      <c r="L19" s="17">
+        <f>ROUND(0.8*K19,0)</f>
+        <v>16</v>
+      </c>
+      <c r="M19" s="17">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O19" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>15</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8">
+        <v>0</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0</v>
+      </c>
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
+      <c r="L20" s="8">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="4"/>
+      <c r="O20" s="7"/>
+    </row>
+    <row r="22" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>30</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="22" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>31</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -1375,14 +1607,15 @@
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:O2"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A1:P2"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A22:O22"/>
   </mergeCells>
-  <conditionalFormatting sqref="K6:K16 K18:K20">
+  <conditionalFormatting sqref="L6:M6 L18:L20 L7:L16 M7:M20">
     <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
       <formula>12</formula>
     </cfRule>
@@ -1390,28 +1623,25 @@
       <formula>16</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6:M20">
+  <conditionalFormatting sqref="N6:N20">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>M6="Įskaityta"</formula>
+      <formula>N6="Įskaityta"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>M6="Neįskaityta"</formula>
+      <formula>N6="Neįskaityta"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>M6="Persilaikyti"</formula>
+      <formula>N6="Persilaikyti"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C6:C20" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1. Tyrimas,2. n8n automatizacija,2. Vibe-coding"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H6:H11 H13:H16 G18:J20 I6:J16 G6:G16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H6:K17 G18:K20 G6:G16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L6:L20" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"Taip,Ne,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="M6:M20" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="N6:N20" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Įskaityta,Neįskaityta,Persilaikyti"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1431,174 +1661,174 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1" s="12"/>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="15"/>
+    </row>
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="15"/>
-    </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="B5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="7" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+    </row>
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-    </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="7" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="7" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="7" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="15"/>
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="15"/>
-    </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="7" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="15"/>
+    </row>
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="15"/>
-    </row>
-    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="7" t="s">
+    </row>
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="15"/>
+    </row>
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="15"/>
-    </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="7" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="15"/>
+    </row>
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="15"/>
-    </row>
-    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="7" t="s">
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="7" t="s">
+    </row>
+    <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="7" t="s">
+    </row>
+    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
